--- a/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,77</t>
+          <t>-6,34; -0,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,0</t>
+          <t>-5,7; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,41</t>
+          <t>-0,51; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,45</t>
+          <t>-0,91; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,25</t>
+          <t>-0,78; 0,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,11</t>
+          <t>-0,73; 0,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 338,04</t>
+          <t>-100,0; 347,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -0,76</t>
+          <t>-6,27; -0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,0</t>
+          <t>-5,09; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,53</t>
+          <t>-0,51; 0,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,0</t>
+          <t>-0,91; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,46</t>
+          <t>-1,29; 1,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,24</t>
+          <t>-0,78; 0,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,13</t>
+          <t>-0,75; 0,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 347,26</t>
+          <t>-100,0; 260,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -0,77</t>
+          <t>-7,29; -0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,0</t>
+          <t>-5,58; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,45</t>
+          <t>-0,51; 0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-0,76; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,47</t>
+          <t>-0,91; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,15</t>
+          <t>-0,73; 0,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,13</t>
+          <t>-0,72; 0,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 260,53</t>
+          <t>-100,0; 338,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1004-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-2.353633090101663</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.026437965786552</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,29; -0,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,58; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.290925137801013</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.583172324478164</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-0.7719082701257663</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,51; 0,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 0,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,94</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>-0.07810595115140902</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1511900171612496</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2880151907173348</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3075213619228613</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.5099134141626507</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.7550138860275577</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,98</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 1,45</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4059262396664125</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9420444623053107</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +739,139 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-53,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-64,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3925849975539448</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02481082702124517</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.05474749797084145</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 0,25</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 0,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,79</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 338,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.9109159679810677</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.975829261195323</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.44982816100149</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.2431137708797486</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.20651835907575</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1931179874601953</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.5391563709573964</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.6487864657980665</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7282660774060742</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.7200704416882342</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2466615943275207</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1124147105825184</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.7915691186436604</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.380370587297258</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +880,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
